--- a/src/main/resources/APR_Report.xlsx
+++ b/src/main/resources/APR_Report.xlsx
@@ -9,12 +9,9 @@
   <sheets>
     <sheet name="APR Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -436,15 +433,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="14.0"/>
-    <col min="2" max="2" customWidth="true" width="10.0"/>
-    <col min="3" max="3" customWidth="true" width="10.0"/>
-    <col min="4" max="4" customWidth="true" width="12.0"/>
-    <col min="5" max="5" customWidth="true" width="14.0"/>
-    <col min="6" max="6" customWidth="true" width="14.0"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,19 +499,19 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ACC00002</t>
+          <t>ACC00001</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1051</v>
+        <v>0.0599</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>421.92</v>
+        <v>581.15</v>
       </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -522,19 +519,19 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ACC00002</t>
+          <t>ACC00001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2999</v>
+        <v>0.0634</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>29.8</v>
+        <v>194.75</v>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n"/>
@@ -542,19 +539,19 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ACC00003</t>
+          <t>ACC00002</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.16079999999999997</v>
+        <v>0.1051</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>561.25</v>
+        <v>421.92</v>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -562,19 +559,19 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ACC00003</t>
+          <t>ACC00002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2823</v>
+        <v>0.2999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>716.02</v>
+        <v>29.8</v>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -582,19 +579,19 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ACC00004</t>
+          <t>ACC00002</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.244</v>
+        <v>0.0599</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>159.66</v>
+        <v>965.25</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="3" t="n"/>
@@ -602,19 +599,19 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ACC00004</t>
+          <t>ACC00002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.1573</v>
+        <v>0.0634</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>422.61</v>
+        <v>923.98</v>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="3" t="n"/>
@@ -622,19 +619,19 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ACC00004</t>
+          <t>ACC00003</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.2582</v>
+        <v>0.1608</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>277.87</v>
+        <v>561.25</v>
       </c>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="3" t="n"/>
@@ -642,19 +639,19 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ACC00004</t>
+          <t>ACC00003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.1816</v>
+        <v>0.2823</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>215.31</v>
+        <v>716.02</v>
       </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -662,7 +659,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ACC00004</t>
+          <t>ACC00003</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -674,7 +671,7 @@
         <v>0.0599</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>763.49</v>
+        <v>467.14</v>
       </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="3" t="n"/>
@@ -682,19 +679,19 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ACC00005</t>
+          <t>ACC00003</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>358.98</v>
+        <v>663.47</v>
       </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -702,19 +699,19 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ACC00006</t>
+          <t>ACC00004</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1745</v>
+        <v>0.244</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>973.12</v>
+        <v>159.66</v>
       </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="3" t="n"/>
@@ -722,19 +719,19 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ACC00006</t>
+          <t>ACC00004</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>378.53</v>
+        <v>422.61</v>
       </c>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -742,19 +739,19 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ACC00006</t>
+          <t>ACC00004</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.2616</v>
+        <v>0.2582</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>552.04</v>
+        <v>277.87</v>
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
@@ -762,19 +759,19 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ACC00007</t>
+          <t>ACC00004</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.21989999999999998</v>
+        <v>0.1816</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>985.22</v>
+        <v>215.31</v>
       </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -782,19 +779,19 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ACC00007</t>
+          <t>ACC00004</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.1434</v>
+        <v>0.0599</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>855.3200000000001</v>
+        <v>763.49</v>
       </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="3" t="n"/>
@@ -802,19 +799,19 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACC00007</t>
+          <t>ACC00004</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.0877</v>
+        <v>0.0634</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>866.48</v>
+        <v>214.52</v>
       </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -822,19 +819,19 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ACC00007</t>
+          <t>ACC00005</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>380.13</v>
+        <v>358.98</v>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="3" t="n"/>
@@ -842,19 +839,19 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ACC00007</t>
+          <t>ACC00005</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.16079999999999997</v>
+        <v>0.0599</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>453.41</v>
+        <v>221.7</v>
       </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -862,19 +859,19 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ACC00008</t>
+          <t>ACC00005</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.1295</v>
+        <v>0.0634</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>266.98</v>
+        <v>288.52</v>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="3" t="n"/>
@@ -882,19 +879,19 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ACC00008</t>
+          <t>ACC00006</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.2232</v>
+        <v>0.1745</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>936.65</v>
+        <v>973.12</v>
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -902,19 +899,19 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ACC00008</t>
+          <t>ACC00006</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.2164</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>648.04</v>
+        <v>378.53</v>
       </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="3" t="n"/>
@@ -922,19 +919,19 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ACC00009</t>
+          <t>ACC00006</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.1329</v>
+        <v>0.2616</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>989.52</v>
+        <v>552.04</v>
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="3" t="n"/>
@@ -942,19 +939,19 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ACC00009</t>
+          <t>ACC00006</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.2964</v>
+        <v>0.0599</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>640</v>
+        <v>692.42</v>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="3" t="n"/>
@@ -962,19 +959,19 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ACC00009</t>
+          <t>ACC00006</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.1677</v>
+        <v>0.0634</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>556.95</v>
+        <v>212.38</v>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="3" t="n"/>
@@ -982,19 +979,19 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ACC00009</t>
+          <t>ACC00007</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.1295</v>
+        <v>0.2199</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>684.61</v>
+        <v>985.22</v>
       </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="3" t="n"/>
@@ -1002,19 +999,19 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ACC00009</t>
+          <t>ACC00007</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.2651</v>
+        <v>0.1434</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>842.85</v>
+        <v>855.3200000000001</v>
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="3" t="n"/>
@@ -1022,19 +1019,19 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ACC00010</t>
+          <t>ACC00007</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.16079999999999997</v>
+        <v>0.0877</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>805.05</v>
+        <v>866.48</v>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="3" t="n"/>
@@ -1042,19 +1039,19 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ACC00011</t>
+          <t>ACC00007</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.1782</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>499.23</v>
+        <v>380.13</v>
       </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="3" t="n"/>
@@ -1062,19 +1059,19 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ACC00011</t>
+          <t>ACC00007</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.0877</v>
+        <v>0.1608</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>884.6799999999999</v>
+        <v>453.41</v>
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="3" t="n"/>
@@ -1082,19 +1079,19 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ACC00011</t>
+          <t>ACC00007</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.1536</v>
+        <v>0.0599</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>642.85</v>
+        <v>971.11</v>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="3" t="n"/>
@@ -1102,19 +1099,19 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ACC00011</t>
+          <t>ACC00007</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.19899999999999998</v>
+        <v>0.0634</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>142.87</v>
+        <v>70.36</v>
       </c>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="3" t="n"/>
@@ -1122,19 +1119,19 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ACC00012</t>
+          <t>ACC00008</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.1677</v>
+        <v>0.1295</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>584.59</v>
+        <v>266.98</v>
       </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="3" t="n"/>
@@ -1142,19 +1139,19 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ACC00012</t>
+          <t>ACC00008</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.2964</v>
+        <v>0.2232</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>897.8200000000001</v>
+        <v>936.65</v>
       </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="3" t="n"/>
@@ -1162,19 +1159,19 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ACC00013</t>
+          <t>ACC00008</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.21989999999999998</v>
+        <v>0.2164</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>755.78</v>
+        <v>648.04</v>
       </c>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="3" t="n"/>
@@ -1182,19 +1179,19 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ACC00013</t>
+          <t>ACC00008</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.1573</v>
+        <v>0.0599</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>861.1</v>
+        <v>193.29</v>
       </c>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="3" t="n"/>
@@ -1202,19 +1199,19 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ACC00013</t>
+          <t>ACC00008</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.11900000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>152.84</v>
+        <v>88.86</v>
       </c>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="3" t="n"/>
@@ -1222,19 +1219,19 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ACC00013</t>
+          <t>ACC00009</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.28600000000000003</v>
+        <v>0.1329</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>159.98</v>
+        <v>989.52</v>
       </c>
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="3" t="n"/>
@@ -1242,19 +1239,19 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ACC00014</t>
+          <t>ACC00009</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.0877</v>
+        <v>0.2964</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>971.08</v>
+        <v>640</v>
       </c>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="3" t="n"/>
@@ -1262,19 +1259,19 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ACC00014</t>
+          <t>ACC00009</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.2303</v>
+        <v>0.1677</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>860.78</v>
+        <v>556.95</v>
       </c>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="3" t="n"/>
@@ -1282,19 +1279,19 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ACC00014</t>
+          <t>ACC00009</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.22690000000000002</v>
+        <v>0.1295</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>11.48</v>
+        <v>684.61</v>
       </c>
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="3" t="n"/>
@@ -1302,7 +1299,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ACC00014</t>
+          <t>ACC00009</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1314,7 +1311,7 @@
         <v>0.2651</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>720.72</v>
+        <v>842.85</v>
       </c>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="3" t="n"/>
@@ -1322,19 +1319,19 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ACC00015</t>
+          <t>ACC00009</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1782</v>
+        <v>0.0599</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>3.25</v>
+        <v>769.89</v>
       </c>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -1342,19 +1339,19 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ACC00015</t>
+          <t>ACC00009</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.2095</v>
+        <v>0.0634</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>722.09</v>
+        <v>366.51</v>
       </c>
       <c r="E45" s="2" t="n"/>
       <c r="F45" s="3" t="n"/>
@@ -1362,19 +1359,19 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ACC00015</t>
+          <t>ACC00010</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.10859999999999999</v>
+        <v>0.1608</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>719.6799999999999</v>
+        <v>805.05</v>
       </c>
       <c r="E46" s="2" t="n"/>
       <c r="F46" s="3" t="n"/>
@@ -1382,19 +1379,19 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ACC00015</t>
+          <t>ACC00010</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.1886</v>
+        <v>0.0599</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>971.89</v>
+        <v>471.68</v>
       </c>
       <c r="E47" s="2" t="n"/>
       <c r="F47" s="3" t="n"/>
@@ -1402,19 +1399,19 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ACC00015</t>
+          <t>ACC00010</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.25120000000000003</v>
+        <v>0.0634</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>761.96</v>
+        <v>326.03</v>
       </c>
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="3" t="n"/>
@@ -1422,19 +1419,19 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ACC00016</t>
+          <t>ACC00011</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.1051</v>
+        <v>0.1782</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>161.55</v>
+        <v>499.23</v>
       </c>
       <c r="E49" s="2" t="n"/>
       <c r="F49" s="3" t="n"/>
@@ -1442,19 +1439,19 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ACC00016</t>
+          <t>ACC00011</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.19210000000000002</v>
+        <v>0.0877</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>953.5</v>
+        <v>884.6799999999999</v>
       </c>
       <c r="E50" s="2" t="n"/>
       <c r="F50" s="3" t="n"/>
@@ -1462,19 +1459,19 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ACC00016</t>
+          <t>ACC00011</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.2823</v>
+        <v>0.1536</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>922.4299999999999</v>
+        <v>642.85</v>
       </c>
       <c r="E51" s="2" t="n"/>
       <c r="F51" s="3" t="n"/>
@@ -1482,19 +1479,19 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ACC00016</t>
+          <t>ACC00011</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.1469</v>
+        <v>0.199</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>918.49</v>
+        <v>142.87</v>
       </c>
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="3" t="n"/>
@@ -1502,19 +1499,19 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ACC00016</t>
+          <t>ACC00011</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0.126</v>
+        <v>0.0599</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>598.9400000000001</v>
+        <v>637.4299999999999</v>
       </c>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="3" t="n"/>
@@ -1522,19 +1519,19 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ACC00017</t>
+          <t>ACC00011</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.0669</v>
+        <v>0.0634</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>240.87</v>
+        <v>403.89</v>
       </c>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="3" t="n"/>
@@ -1542,19 +1539,19 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ACC00017</t>
+          <t>ACC00012</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0.10859999999999999</v>
+        <v>0.1677</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>567.36</v>
+        <v>584.59</v>
       </c>
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="3" t="n"/>
@@ -1562,19 +1559,19 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ACC00017</t>
+          <t>ACC00012</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.21989999999999998</v>
+        <v>0.2964</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>78.76000000000001</v>
+        <v>897.8200000000001</v>
       </c>
       <c r="E56" s="2" t="n"/>
       <c r="F56" s="3" t="n"/>
@@ -1582,19 +1579,19 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ACC00017</t>
+          <t>ACC00012</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.1956</v>
+        <v>0.0599</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>731.91</v>
+        <v>208.27</v>
       </c>
       <c r="E57" s="2" t="n"/>
       <c r="F57" s="3" t="n"/>
@@ -1602,19 +1599,19 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ACC00018</t>
+          <t>ACC00012</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.2964</v>
+        <v>0.0634</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>128.39</v>
+        <v>430.15</v>
       </c>
       <c r="E58" s="2" t="n"/>
       <c r="F58" s="3" t="n"/>
@@ -1622,123 +1619,99 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ACC00019</t>
+          <t>ACC00013</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.1329</v>
+        <v>0.2199</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>755.27</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0.0688</v>
-      </c>
+        <v>755.78</v>
+      </c>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ACC00019</t>
+          <t>ACC00013</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.1747</v>
+        <v>0.1573</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>689.87</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>0.0688</v>
-      </c>
+        <v>861.1</v>
+      </c>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ACC00019</t>
+          <t>ACC00013</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.2929</v>
+        <v>0.119</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>712.95</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>0.0688</v>
-      </c>
+        <v>152.84</v>
+      </c>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ACC00019</t>
+          <t>ACC00013</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.2477</v>
+        <v>0.286</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>398.99</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>0.0688</v>
-      </c>
+        <v>159.98</v>
+      </c>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ACC00020</t>
+          <t>ACC00013</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.2545</v>
+        <v>0.0599</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>224.7</v>
+        <v>304.29</v>
       </c>
       <c r="E63" s="2" t="n"/>
       <c r="F63" s="3" t="n"/>
@@ -1746,19 +1719,19 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ACC00020</t>
+          <t>ACC00013</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.2895</v>
+        <v>0.0634</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>338.09</v>
+        <v>110.8</v>
       </c>
       <c r="E64" s="2" t="n"/>
       <c r="F64" s="3" t="n"/>
@@ -1766,19 +1739,19 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ACC00020</t>
+          <t>ACC00014</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0.2582</v>
+        <v>0.0877</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>588.3099999999999</v>
+        <v>971.08</v>
       </c>
       <c r="E65" s="2" t="n"/>
       <c r="F65" s="3" t="n"/>
@@ -1786,19 +1759,19 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ACC00021</t>
+          <t>ACC00014</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.1573</v>
+        <v>0.2303</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>631.1</v>
+        <v>860.78</v>
       </c>
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="3" t="n"/>
@@ -1806,19 +1779,19 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ACC00021</t>
+          <t>ACC00014</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.2269</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>228.94</v>
+        <v>11.48</v>
       </c>
       <c r="E67" s="2" t="n"/>
       <c r="F67" s="3" t="n"/>
@@ -1826,19 +1799,19 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ACC00022</t>
+          <t>ACC00014</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.20600000000000002</v>
+        <v>0.2651</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>238</v>
+        <v>720.72</v>
       </c>
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="3" t="n"/>
@@ -1846,19 +1819,19 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ACC00023</t>
+          <t>ACC00014</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0.1536</v>
+        <v>0.0599</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>472.97</v>
+        <v>823.39</v>
       </c>
       <c r="E69" s="2" t="n"/>
       <c r="F69" s="3" t="n"/>
@@ -1866,19 +1839,19 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ACC00023</t>
+          <t>ACC00014</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.2999</v>
+        <v>0.0634</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>407.06</v>
+        <v>680.15</v>
       </c>
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="3" t="n"/>
@@ -1886,19 +1859,19 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ACC00023</t>
+          <t>ACC00015</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.11560000000000001</v>
+        <v>0.1782</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>94.33</v>
+        <v>3.25</v>
       </c>
       <c r="E71" s="2" t="n"/>
       <c r="F71" s="3" t="n"/>
@@ -1906,19 +1879,19 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ACC00023</t>
+          <t>ACC00015</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.2686</v>
+        <v>0.2095</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>658.98</v>
+        <v>722.09</v>
       </c>
       <c r="E72" s="2" t="n"/>
       <c r="F72" s="3" t="n"/>
@@ -1926,97 +1899,79 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ACC00024</t>
+          <t>ACC00015</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>0.2477</v>
+        <v>0.1086</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>SCRA</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>719.6799999999999</v>
+      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ACC00024</t>
+          <t>ACC00015</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.2408</v>
+        <v>0.1886</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>653.46</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>SCRA</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>971.89</v>
+      </c>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ACC00024</t>
+          <t>ACC00015</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.2651</v>
+        <v>0.2512</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>646.1799999999999</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>SCRA</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>761.96</v>
+      </c>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ACC00025</t>
+          <t>ACC00015</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.2373</v>
+        <v>0.0599</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>800.59</v>
+        <v>664.79</v>
       </c>
       <c r="E76" s="2" t="n"/>
       <c r="F76" s="3" t="n"/>
@@ -2024,19 +1979,19 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ACC00026</t>
+          <t>ACC00015</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>0.1677</v>
+        <v>0.0634</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>536.29</v>
+        <v>882.45</v>
       </c>
       <c r="E77" s="2" t="n"/>
       <c r="F77" s="3" t="n"/>
@@ -2044,19 +1999,19 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ACC00027</t>
+          <t>ACC00016</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0.2477</v>
+        <v>0.1051</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>249.81</v>
+        <v>161.55</v>
       </c>
       <c r="E78" s="2" t="n"/>
       <c r="F78" s="3" t="n"/>
@@ -2064,19 +2019,19 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ACC00027</t>
+          <t>ACC00016</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0.1399</v>
+        <v>0.1921</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>923.27</v>
+        <v>953.5</v>
       </c>
       <c r="E79" s="2" t="n"/>
       <c r="F79" s="3" t="n"/>
@@ -2084,357 +2039,279 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ACC00028</t>
+          <t>ACC00016</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.1016</v>
+        <v>0.2823</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>848.7</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>0.0329</v>
-      </c>
+        <v>922.4299999999999</v>
+      </c>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ACC00028</t>
+          <t>ACC00016</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>0.0808</v>
+        <v>0.1469</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>166.31</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>0.0329</v>
-      </c>
+        <v>918.49</v>
+      </c>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ACC00028</t>
+          <t>ACC00016</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.2999</v>
+        <v>0.126</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>485.64</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>0.0329</v>
-      </c>
+        <v>598.9400000000001</v>
+      </c>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ACC00028</t>
+          <t>ACC00016</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>0.0634</v>
+        <v>0.0599</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>213.75</v>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>0.0329</v>
-      </c>
+        <v>394.64</v>
+      </c>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ACC00029</t>
+          <t>ACC00016</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>0.0842</v>
+        <v>0.0634</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>784.0700000000001</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>0.040999999999999995</v>
-      </c>
+        <v>379.28</v>
+      </c>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ACC00029</t>
+          <t>ACC00017</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.1329</v>
+        <v>0.0669</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>455.01</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0.040999999999999995</v>
-      </c>
+        <v>240.87</v>
+      </c>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ACC00029</t>
+          <t>ACC00017</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.2269</v>
+        <v>0.1086</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>423.01</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0.040999999999999995</v>
-      </c>
+        <v>567.36</v>
+      </c>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>ACC00029</t>
+          <t>ACC00017</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.2199</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>957.3200000000001</v>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.040999999999999995</v>
-      </c>
+        <v>78.76000000000001</v>
+      </c>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ACC00030</t>
+          <t>ACC00017</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0.2756</v>
+        <v>0.1956</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>542.2</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.07629999999999999</v>
-      </c>
+        <v>731.91</v>
+      </c>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ACC00030</t>
+          <t>ACC00017</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>0.126</v>
+        <v>0.0599</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>747.98</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0.07629999999999999</v>
-      </c>
+        <v>422.97</v>
+      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ACC00030</t>
+          <t>ACC00017</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
-        <v>0.1434</v>
+        <v>0.0634</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>57.17</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>0.07629999999999999</v>
-      </c>
+        <v>404.55</v>
+      </c>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ACC00030</t>
+          <t>ACC00018</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0.1886</v>
+        <v>0.2964</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>584.1799999999999</v>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>0.07629999999999999</v>
-      </c>
+        <v>128.39</v>
+      </c>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ACC00030</t>
+          <t>ACC00018</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.1538</v>
+        <v>0.0599</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>502.85</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>0.07629999999999999</v>
-      </c>
+        <v>668.9400000000001</v>
+      </c>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ACC00031</t>
+          <t>ACC00018</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
-        <v>0.1295</v>
+        <v>0.0634</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>67.95999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="E93" s="2" t="n"/>
       <c r="F93" s="3" t="n"/>
@@ -2442,99 +2319,123 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ACC00031</t>
+          <t>ACC00019</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.08410000000000001</v>
+        <v>0.1329</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>861.8200000000001</v>
-      </c>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="3" t="n"/>
+        <v>755.27</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.0688</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ACC00031</t>
+          <t>ACC00019</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
-        <v>0.28600000000000003</v>
+        <v>0.1747</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>403.78</v>
-      </c>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="3" t="n"/>
+        <v>689.87</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0.0688</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ACC00031</t>
+          <t>ACC00019</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.09449999999999999</v>
+        <v>0.2929</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>941.6</v>
-      </c>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="3" t="n"/>
+        <v>712.95</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.0688</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ACC00031</t>
+          <t>ACC00019</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.1399</v>
+        <v>0.2477</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>569.6799999999999</v>
-      </c>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="3" t="n"/>
+        <v>398.99</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.0688</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ACC00032</t>
+          <t>ACC00019</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.0599</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>716.1900000000001</v>
+        <v>464.11</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -2542,25 +2443,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.054000000000000006</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ACC00032</t>
+          <t>ACC00019</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>238.69</v>
+        <v>535.08</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -2568,39 +2469,33 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.054000000000000006</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ACC00032</t>
+          <t>ACC00020</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.2442</v>
+        <v>0.2545</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>395.79</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>0.054000000000000006</v>
-      </c>
+        <v>224.7</v>
+      </c>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ACC00032</t>
+          <t>ACC00020</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2612,59 +2507,47 @@
         <v>0.2895</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>671.6900000000001</v>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>0.054000000000000006</v>
-      </c>
+        <v>338.09</v>
+      </c>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ACC00032</t>
+          <t>ACC00020</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
-        <v>0.199</v>
+        <v>0.2582</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>0.054000000000000006</v>
-      </c>
+        <v>588.3099999999999</v>
+      </c>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ACC00033</t>
+          <t>ACC00020</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0.09119999999999999</v>
+        <v>0.0599</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>562.99</v>
+        <v>345.51</v>
       </c>
       <c r="E103" s="2" t="n"/>
       <c r="F103" s="3" t="n"/>
@@ -2672,7 +2555,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ACC00033</t>
+          <t>ACC00020</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2684,7 +2567,7 @@
         <v>0.0634</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>99.98</v>
+        <v>21.87</v>
       </c>
       <c r="E104" s="2" t="n"/>
       <c r="F104" s="3" t="n"/>
@@ -2692,19 +2575,19 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ACC00033</t>
+          <t>ACC00021</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
-        <v>0.2616</v>
+        <v>0.1573</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>537.63</v>
+        <v>631.1</v>
       </c>
       <c r="E105" s="2" t="n"/>
       <c r="F105" s="3" t="n"/>
@@ -2712,19 +2595,19 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ACC00034</t>
+          <t>ACC00021</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.1745</v>
+        <v>0.0599</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>157.75</v>
+        <v>228.94</v>
       </c>
       <c r="E106" s="2" t="n"/>
       <c r="F106" s="3" t="n"/>
@@ -2732,19 +2615,19 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ACC00034</t>
+          <t>ACC00021</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.11560000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>833.74</v>
+        <v>704.6</v>
       </c>
       <c r="E107" s="2" t="n"/>
       <c r="F107" s="3" t="n"/>
@@ -2752,19 +2635,19 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ACC00034</t>
+          <t>ACC00022</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0.21289999999999998</v>
+        <v>0.206</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>703.54</v>
+        <v>238</v>
       </c>
       <c r="E108" s="2" t="n"/>
       <c r="F108" s="3" t="n"/>
@@ -2772,19 +2655,19 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ACC00034</t>
+          <t>ACC00022</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>0.0877</v>
+        <v>0.0599</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>611.6799999999999</v>
+        <v>9.44</v>
       </c>
       <c r="E109" s="2" t="n"/>
       <c r="F109" s="3" t="n"/>
@@ -2792,19 +2675,19 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>ACC00034</t>
+          <t>ACC00022</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0.1677</v>
+        <v>0.0634</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>987.23</v>
+        <v>564.41</v>
       </c>
       <c r="E110" s="2" t="n"/>
       <c r="F110" s="3" t="n"/>
@@ -2812,19 +2695,19 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>ACC00035</t>
+          <t>ACC00023</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0.0634</v>
+        <v>0.1536</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>107.04</v>
+        <v>472.97</v>
       </c>
       <c r="E111" s="2" t="n"/>
       <c r="F111" s="3" t="n"/>
@@ -2832,19 +2715,19 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ACC00035</t>
+          <t>ACC00023</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0.19210000000000002</v>
+        <v>0.2999</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>553.22</v>
+        <v>407.06</v>
       </c>
       <c r="E112" s="2" t="n"/>
       <c r="F112" s="3" t="n"/>
@@ -2852,19 +2735,19 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ACC00035</t>
+          <t>ACC00023</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0.1051</v>
+        <v>0.1156</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>272.35</v>
+        <v>94.33</v>
       </c>
       <c r="E113" s="2" t="n"/>
       <c r="F113" s="3" t="n"/>
@@ -2872,19 +2755,19 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ACC00035</t>
+          <t>ACC00023</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0.11900000000000001</v>
+        <v>0.2686</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>604.83</v>
+        <v>658.98</v>
       </c>
       <c r="E114" s="2" t="n"/>
       <c r="F114" s="3" t="n"/>
@@ -2892,19 +2775,19 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ACC00035</t>
+          <t>ACC00023</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0.1745</v>
+        <v>0.0599</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>717.61</v>
+        <v>153.37</v>
       </c>
       <c r="E115" s="2" t="n"/>
       <c r="F115" s="3" t="n"/>
@@ -2912,19 +2795,19 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ACC00036</t>
+          <t>ACC00023</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0.1745</v>
+        <v>0.0634</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>905.34</v>
+        <v>34.58</v>
       </c>
       <c r="E116" s="2" t="n"/>
       <c r="F116" s="3" t="n"/>
@@ -2932,119 +2815,149 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ACC00036</t>
+          <t>ACC00024</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
-        <v>0.2823</v>
+        <v>0.2477</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>846.1</v>
-      </c>
-      <c r="E117" s="2" t="n"/>
-      <c r="F117" s="3" t="n"/>
+        <v>54.17</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ACC00037</t>
+          <t>ACC00024</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.2477</v>
+        <v>0.2408</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>44.09</v>
-      </c>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="3" t="n"/>
+        <v>653.46</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ACC00038</t>
+          <t>ACC00024</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>0.11560000000000001</v>
+        <v>0.2651</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>551.6799999999999</v>
-      </c>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="3" t="n"/>
+        <v>646.1799999999999</v>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ACC00038</t>
+          <t>ACC00024</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0.1745</v>
+        <v>0.0599</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>427.69</v>
-      </c>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="3" t="n"/>
+        <v>180.84</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ACC00038</t>
+          <t>ACC00024</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0.1295</v>
+        <v>0.0634</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="E121" s="2" t="n"/>
-      <c r="F121" s="3" t="n"/>
+        <v>65.73999999999999</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ACC00039</t>
+          <t>ACC00025</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>0.126</v>
+        <v>0.2373</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>834.6</v>
+        <v>800.59</v>
       </c>
       <c r="E122" s="2" t="n"/>
       <c r="F122" s="3" t="n"/>
@@ -3052,19 +2965,19 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ACC00040</t>
+          <t>ACC00025</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0.1225</v>
+        <v>0.0599</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>933.09</v>
+        <v>150.76</v>
       </c>
       <c r="E123" s="2" t="n"/>
       <c r="F123" s="3" t="n"/>
@@ -3072,19 +2985,19 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ACC00040</t>
+          <t>ACC00025</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0.25120000000000003</v>
+        <v>0.0634</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>972.2</v>
+        <v>684.87</v>
       </c>
       <c r="E124" s="2" t="n"/>
       <c r="F124" s="3" t="n"/>
@@ -3092,19 +3005,19 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ACC00040</t>
+          <t>ACC00026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0.11560000000000001</v>
+        <v>0.1677</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>39.89</v>
+        <v>536.29</v>
       </c>
       <c r="E125" s="2" t="n"/>
       <c r="F125" s="3" t="n"/>
@@ -3112,19 +3025,19 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ACC00040</t>
+          <t>ACC00026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.0599</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>357.81</v>
+        <v>728.28</v>
       </c>
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="3" t="n"/>
@@ -3132,19 +3045,19 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ACC00040</t>
+          <t>ACC00026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
-        <v>0.1956</v>
+        <v>0.0634</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>682.0700000000001</v>
+        <v>362.78</v>
       </c>
       <c r="E127" s="2" t="n"/>
       <c r="F127" s="3" t="n"/>
@@ -3152,19 +3065,19 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ACC00041</t>
+          <t>ACC00027</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0.2164</v>
+        <v>0.2477</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>884.13</v>
+        <v>249.81</v>
       </c>
       <c r="E128" s="2" t="n"/>
       <c r="F128" s="3" t="n"/>
@@ -3172,449 +3085,521 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>ACC00042</t>
+          <t>ACC00027</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>0.126</v>
+        <v>0.1399</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>SCRA</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>923.27</v>
+      </c>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ACC00042</t>
+          <t>ACC00027</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.1642</v>
+        <v>0.0599</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>736.5599999999999</v>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>SCRA</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>652.39</v>
+      </c>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>ACC00042</t>
+          <t>ACC00027</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>0.1295</v>
+        <v>0.0634</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>332.19</v>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>SCRA</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>0.06</v>
-      </c>
+        <v>475.13</v>
+      </c>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ACC00042</t>
+          <t>ACC00028</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0.1364</v>
+        <v>0.1016</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>930.8200000000001</v>
+        <v>848.7</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>SCRA</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0.06</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>ACC00043</t>
+          <t>ACC00028</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>0.1782</v>
+        <v>0.0808</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>108.1</v>
-      </c>
-      <c r="E133" s="2" t="n"/>
-      <c r="F133" s="3" t="n"/>
+        <v>166.31</v>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.0329</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ACC00043</t>
+          <t>ACC00028</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0.1295</v>
+        <v>0.2999</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>872.17</v>
-      </c>
-      <c r="E134" s="2" t="n"/>
-      <c r="F134" s="3" t="n"/>
+        <v>485.64</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0.0329</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ACC00044</t>
+          <t>ACC00028</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.1573</v>
+        <v>0.0634</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>795.35</v>
-      </c>
-      <c r="E135" s="2" t="n"/>
-      <c r="F135" s="3" t="n"/>
+        <v>213.75</v>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>0.0329</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ACC00044</t>
+          <t>ACC00028</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>0.1469</v>
+        <v>0.0599</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>227.6</v>
-      </c>
-      <c r="E136" s="2" t="n"/>
-      <c r="F136" s="3" t="n"/>
+        <v>498.45</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>0.0329</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ACC00044</t>
+          <t>ACC00029</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
-        <v>0.2616</v>
+        <v>0.0842</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="E137" s="2" t="n"/>
-      <c r="F137" s="3" t="n"/>
+        <v>784.0700000000001</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>0.04099999999999999</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ACC00044</t>
+          <t>ACC00029</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>0.21289999999999998</v>
+        <v>0.1329</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>193.13</v>
-      </c>
-      <c r="E138" s="2" t="n"/>
-      <c r="F138" s="3" t="n"/>
+        <v>455.01</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>0.04099999999999999</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>ACC00045</t>
+          <t>ACC00029</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
-        <v>0.1816</v>
+        <v>0.2269</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>399.68</v>
-      </c>
-      <c r="E139" s="2" t="n"/>
-      <c r="F139" s="3" t="n"/>
+        <v>423.01</v>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>0.04099999999999999</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>ACC00045</t>
+          <t>ACC00029</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>0.0877</v>
+        <v>0.0599</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>981.15</v>
-      </c>
-      <c r="E140" s="2" t="n"/>
-      <c r="F140" s="3" t="n"/>
+        <v>957.3200000000001</v>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>0.04099999999999999</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>ACC00045</t>
+          <t>ACC00029</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>0.21289999999999998</v>
+        <v>0.0634</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>536.22</v>
-      </c>
-      <c r="E141" s="2" t="n"/>
-      <c r="F141" s="3" t="n"/>
+        <v>875.9</v>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>0.04099999999999999</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>ACC00046</t>
+          <t>ACC00030</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
-        <v>0.1086</v>
+        <v>0.2756</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>261.22</v>
+        <v>542.2</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>SCRA</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07629999999999999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>ACC00047</t>
+          <t>ACC00030</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
-        <v>0.1745</v>
+        <v>0.126</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>313.68</v>
-      </c>
-      <c r="E143" s="2" t="n"/>
-      <c r="F143" s="3" t="n"/>
+        <v>747.98</v>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>0.07629999999999999</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>ACC00047</t>
+          <t>ACC00030</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
-        <v>0.0738</v>
+        <v>0.1434</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>606.21</v>
-      </c>
-      <c r="E144" s="2" t="n"/>
-      <c r="F144" s="3" t="n"/>
+        <v>57.17</v>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>0.07629999999999999</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>ACC00047</t>
+          <t>ACC00030</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
-        <v>0.1051</v>
+        <v>0.1886</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>511.42</v>
-      </c>
-      <c r="E145" s="2" t="n"/>
-      <c r="F145" s="3" t="n"/>
+        <v>584.1799999999999</v>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>0.07629999999999999</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ACC00047</t>
+          <t>ACC00030</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>0.25120000000000003</v>
+        <v>0.1538</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>385.2</v>
-      </c>
-      <c r="E146" s="2" t="n"/>
-      <c r="F146" s="3" t="n"/>
+        <v>502.85</v>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>0.07629999999999999</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ACC00047</t>
+          <t>ACC00030</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
-        <v>0.21289999999999998</v>
+        <v>0.0599</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>576.59</v>
-      </c>
-      <c r="E147" s="2" t="n"/>
-      <c r="F147" s="3" t="n"/>
+        <v>311.29</v>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>0.07629999999999999</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ACC00048</t>
+          <t>ACC00030</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>806.51</v>
-      </c>
-      <c r="E148" s="2" t="n"/>
-      <c r="F148" s="3" t="n"/>
+        <v>869.99</v>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>0.07629999999999999</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ACC00048</t>
+          <t>ACC00031</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
-        <v>0.25120000000000003</v>
+        <v>0.1295</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>686.86</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="E149" s="2" t="n"/>
       <c r="F149" s="3" t="n"/>
@@ -3622,19 +3607,19 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>ACC00048</t>
+          <t>ACC00031</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>940.26</v>
+        <v>861.8200000000001</v>
       </c>
       <c r="E150" s="2" t="n"/>
       <c r="F150" s="3" t="n"/>
@@ -3642,19 +3627,19 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>ACC00049</t>
+          <t>ACC00031</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
-        <v>0.21989999999999998</v>
+        <v>0.286</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>664.24</v>
+        <v>403.78</v>
       </c>
       <c r="E151" s="2" t="n"/>
       <c r="F151" s="3" t="n"/>
@@ -3662,19 +3647,19 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>ACC00049</t>
+          <t>ACC00031</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
-        <v>0.25120000000000003</v>
+        <v>0.09449999999999999</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>330.2</v>
+        <v>941.6</v>
       </c>
       <c r="E152" s="2" t="n"/>
       <c r="F152" s="3" t="n"/>
@@ -3682,19 +3667,19 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>ACC00050</t>
+          <t>ACC00031</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
-        <v>0.1121</v>
+        <v>0.1399</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>408.39</v>
+        <v>569.6799999999999</v>
       </c>
       <c r="E153" s="2" t="n"/>
       <c r="F153" s="3" t="n"/>
@@ -3702,19 +3687,19 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ACC00050</t>
+          <t>ACC00031</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
-        <v>0.19210000000000002</v>
+        <v>0.0599</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>402.4</v>
+        <v>691.08</v>
       </c>
       <c r="E154" s="2" t="n"/>
       <c r="F154" s="3" t="n"/>
@@ -3722,22 +3707,1978 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ACC00050</t>
+          <t>ACC00031</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
-        <v>0.2823</v>
+        <v>0.0634</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>295.66</v>
+        <v>683.46</v>
       </c>
       <c r="E155" s="2" t="n"/>
       <c r="F155" s="3" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>ACC00032</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>0.07730000000000001</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>716.1900000000001</v>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>ACC00032</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="D157" s="4" t="n">
+        <v>238.69</v>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>ACC00032</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>0.2442</v>
+      </c>
+      <c r="D158" s="4" t="n">
+        <v>395.79</v>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ACC00032</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="D159" s="4" t="n">
+        <v>671.6900000000001</v>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>ACC00032</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="D160" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>ACC00032</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>ACC00032</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>84.06</v>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>0.05400000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>ACC00033</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>0.09119999999999999</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>562.99</v>
+      </c>
+      <c r="E163" s="2" t="n"/>
+      <c r="F163" s="3" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ACC00033</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D164" s="4" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="3" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>ACC00033</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>537.63</v>
+      </c>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="3" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>ACC00033</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="E166" s="2" t="n"/>
+      <c r="F166" s="3" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ACC00034</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="D167" s="4" t="n">
+        <v>157.75</v>
+      </c>
+      <c r="E167" s="2" t="n"/>
+      <c r="F167" s="3" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>ACC00034</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>833.74</v>
+      </c>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="3" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ACC00034</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="D169" s="4" t="n">
+        <v>703.54</v>
+      </c>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="3" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ACC00034</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="D170" s="4" t="n">
+        <v>611.6799999999999</v>
+      </c>
+      <c r="E170" s="2" t="n"/>
+      <c r="F170" s="3" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>ACC00034</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>0.1677</v>
+      </c>
+      <c r="D171" s="4" t="n">
+        <v>987.23</v>
+      </c>
+      <c r="E171" s="2" t="n"/>
+      <c r="F171" s="3" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ACC00034</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>345.77</v>
+      </c>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="3" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>ACC00034</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D173" s="4" t="n">
+        <v>946.1</v>
+      </c>
+      <c r="E173" s="2" t="n"/>
+      <c r="F173" s="3" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>ACC00035</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D174" s="4" t="n">
+        <v>107.04</v>
+      </c>
+      <c r="E174" s="2" t="n"/>
+      <c r="F174" s="3" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>ACC00035</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>0.1921</v>
+      </c>
+      <c r="D175" s="4" t="n">
+        <v>553.22</v>
+      </c>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="3" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>ACC00035</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>272.35</v>
+      </c>
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="3" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>ACC00035</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="D177" s="4" t="n">
+        <v>604.83</v>
+      </c>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="3" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>ACC00035</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="D178" s="4" t="n">
+        <v>717.61</v>
+      </c>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="3" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>ACC00035</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D179" s="4" t="n">
+        <v>875.71</v>
+      </c>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="3" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>ACC00036</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="D180" s="4" t="n">
+        <v>905.34</v>
+      </c>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="3" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>ACC00036</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="D181" s="4" t="n">
+        <v>846.1</v>
+      </c>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="3" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>ACC00036</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>838.58</v>
+      </c>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="3" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>ACC00036</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>118.87</v>
+      </c>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="3" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>ACC00037</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>44.09</v>
+      </c>
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="3" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>ACC00037</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D185" s="4" t="n">
+        <v>705.72</v>
+      </c>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="3" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>ACC00037</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D186" s="4" t="n">
+        <v>774.48</v>
+      </c>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="3" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>ACC00038</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="D187" s="4" t="n">
+        <v>551.6799999999999</v>
+      </c>
+      <c r="E187" s="2" t="n"/>
+      <c r="F187" s="3" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>ACC00038</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>427.69</v>
+      </c>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="3" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>ACC00038</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="D189" s="4" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="3" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>ACC00038</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D190" s="4" t="n">
+        <v>809.26</v>
+      </c>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="3" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>ACC00038</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D191" s="4" t="n">
+        <v>792.23</v>
+      </c>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="3" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>ACC00039</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="D192" s="4" t="n">
+        <v>834.6</v>
+      </c>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="3" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>ACC00039</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D193" s="4" t="n">
+        <v>140.32</v>
+      </c>
+      <c r="E193" s="2" t="n"/>
+      <c r="F193" s="3" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>ACC00039</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D194" s="4" t="n">
+        <v>178.83</v>
+      </c>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="3" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>ACC00040</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="D195" s="4" t="n">
+        <v>933.09</v>
+      </c>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="3" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>ACC00040</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="D196" s="4" t="n">
+        <v>972.2</v>
+      </c>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="3" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>ACC00040</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="3" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>ACC00040</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>0.07730000000000001</v>
+      </c>
+      <c r="D198" s="4" t="n">
+        <v>357.81</v>
+      </c>
+      <c r="E198" s="2" t="n"/>
+      <c r="F198" s="3" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>ACC00040</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="D199" s="4" t="n">
+        <v>682.0700000000001</v>
+      </c>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="3" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>ACC00040</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D200" s="4" t="n">
+        <v>792.5599999999999</v>
+      </c>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="3" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>ACC00040</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D201" s="4" t="n">
+        <v>738.22</v>
+      </c>
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="3" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>ACC00041</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>0.2164</v>
+      </c>
+      <c r="D202" s="4" t="n">
+        <v>884.13</v>
+      </c>
+      <c r="E202" s="2" t="n"/>
+      <c r="F202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>ACC00041</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D203" s="4" t="n">
+        <v>892.45</v>
+      </c>
+      <c r="E203" s="2" t="n"/>
+      <c r="F203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>ACC00041</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D204" s="4" t="n">
+        <v>446.48</v>
+      </c>
+      <c r="E204" s="2" t="n"/>
+      <c r="F204" s="3" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>ACC00042</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="D205" s="4" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>ACC00042</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>0.1642</v>
+      </c>
+      <c r="D206" s="4" t="n">
+        <v>736.5599999999999</v>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>ACC00042</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="D207" s="4" t="n">
+        <v>332.19</v>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>ACC00042</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="D208" s="4" t="n">
+        <v>930.8200000000001</v>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ACC00042</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D209" s="4" t="n">
+        <v>889.5700000000001</v>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>ACC00042</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D210" s="4" t="n">
+        <v>139.41</v>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>ACC00043</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="D211" s="4" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="E211" s="2" t="n"/>
+      <c r="F211" s="3" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>ACC00043</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="D212" s="4" t="n">
+        <v>872.17</v>
+      </c>
+      <c r="E212" s="2" t="n"/>
+      <c r="F212" s="3" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>ACC00043</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D213" s="4" t="n">
+        <v>957.12</v>
+      </c>
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="3" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ACC00043</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D214" s="4" t="n">
+        <v>884.47</v>
+      </c>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="3" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>ACC00044</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="D215" s="4" t="n">
+        <v>795.35</v>
+      </c>
+      <c r="E215" s="2" t="n"/>
+      <c r="F215" s="3" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>ACC00044</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="D216" s="4" t="n">
+        <v>227.6</v>
+      </c>
+      <c r="E216" s="2" t="n"/>
+      <c r="F216" s="3" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>ACC00044</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="D217" s="4" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="E217" s="2" t="n"/>
+      <c r="F217" s="3" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>ACC00044</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="D218" s="4" t="n">
+        <v>193.13</v>
+      </c>
+      <c r="E218" s="2" t="n"/>
+      <c r="F218" s="3" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>ACC00044</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D219" s="4" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="E219" s="2" t="n"/>
+      <c r="F219" s="3" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>ACC00044</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D220" s="4" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="E220" s="2" t="n"/>
+      <c r="F220" s="3" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>ACC00045</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="D221" s="4" t="n">
+        <v>399.68</v>
+      </c>
+      <c r="E221" s="2" t="n"/>
+      <c r="F221" s="3" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>ACC00045</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="D222" s="4" t="n">
+        <v>981.15</v>
+      </c>
+      <c r="E222" s="2" t="n"/>
+      <c r="F222" s="3" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>ACC00045</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="D223" s="4" t="n">
+        <v>536.22</v>
+      </c>
+      <c r="E223" s="2" t="n"/>
+      <c r="F223" s="3" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>ACC00045</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D224" s="4" t="n">
+        <v>548.54</v>
+      </c>
+      <c r="E224" s="2" t="n"/>
+      <c r="F224" s="3" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>ACC00045</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D225" s="4" t="n">
+        <v>689.21</v>
+      </c>
+      <c r="E225" s="2" t="n"/>
+      <c r="F225" s="3" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>ACC00046</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>261.22</v>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>ACC00046</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D227" s="4" t="n">
+        <v>350.37</v>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>ACC00046</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D228" s="4" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>SCRA</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>ACC00047</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="D229" s="4" t="n">
+        <v>313.68</v>
+      </c>
+      <c r="E229" s="2" t="n"/>
+      <c r="F229" s="3" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>ACC00047</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="D230" s="4" t="n">
+        <v>606.21</v>
+      </c>
+      <c r="E230" s="2" t="n"/>
+      <c r="F230" s="3" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>ACC00047</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="D231" s="4" t="n">
+        <v>511.42</v>
+      </c>
+      <c r="E231" s="2" t="n"/>
+      <c r="F231" s="3" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>ACC00047</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="D232" s="4" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="E232" s="2" t="n"/>
+      <c r="F232" s="3" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>ACC00047</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="D233" s="4" t="n">
+        <v>576.59</v>
+      </c>
+      <c r="E233" s="2" t="n"/>
+      <c r="F233" s="3" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>ACC00047</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D234" s="4" t="n">
+        <v>278.67</v>
+      </c>
+      <c r="E234" s="2" t="n"/>
+      <c r="F234" s="3" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>ACC00047</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D235" s="4" t="n">
+        <v>824.5</v>
+      </c>
+      <c r="E235" s="2" t="n"/>
+      <c r="F235" s="3" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>ACC00048</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>0.07730000000000001</v>
+      </c>
+      <c r="D236" s="4" t="n">
+        <v>806.51</v>
+      </c>
+      <c r="E236" s="2" t="n"/>
+      <c r="F236" s="3" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>ACC00048</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="D237" s="4" t="n">
+        <v>686.86</v>
+      </c>
+      <c r="E237" s="2" t="n"/>
+      <c r="F237" s="3" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>ACC00048</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D238" s="4" t="n">
+        <v>940.26</v>
+      </c>
+      <c r="E238" s="2" t="n"/>
+      <c r="F238" s="3" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>ACC00048</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D239" s="4" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="E239" s="2" t="n"/>
+      <c r="F239" s="3" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>ACC00049</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>0.2199</v>
+      </c>
+      <c r="D240" s="4" t="n">
+        <v>664.24</v>
+      </c>
+      <c r="E240" s="2" t="n"/>
+      <c r="F240" s="3" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>ACC00049</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="D241" s="4" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="E241" s="2" t="n"/>
+      <c r="F241" s="3" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>ACC00049</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D242" s="4" t="n">
+        <v>937.26</v>
+      </c>
+      <c r="E242" s="2" t="n"/>
+      <c r="F242" s="3" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>ACC00049</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D243" s="4" t="n">
+        <v>250.02</v>
+      </c>
+      <c r="E243" s="2" t="n"/>
+      <c r="F243" s="3" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>ACC00050</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="D244" s="4" t="n">
+        <v>408.39</v>
+      </c>
+      <c r="E244" s="2" t="n"/>
+      <c r="F244" s="3" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>ACC00050</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>0.1921</v>
+      </c>
+      <c r="D245" s="4" t="n">
+        <v>402.4</v>
+      </c>
+      <c r="E245" s="2" t="n"/>
+      <c r="F245" s="3" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>ACC00050</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="D246" s="4" t="n">
+        <v>295.66</v>
+      </c>
+      <c r="E246" s="2" t="n"/>
+      <c r="F246" s="3" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>ACC00050</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D247" s="4" t="n">
+        <v>204.44</v>
+      </c>
+      <c r="E247" s="2" t="n"/>
+      <c r="F247" s="3" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>ACC00050</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D248" s="4" t="n">
+        <v>112.19</v>
+      </c>
+      <c r="E248" s="2" t="n"/>
+      <c r="F248" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/main/resources/APR_Report.xlsx
+++ b/src/main/resources/APR_Report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,14 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,6 +498,46 @@
           <t>OverrideRate</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ProductCode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OriginationDate</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OverrideExpiry</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProtectionStart</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ProtectionEnd</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>DayCountBasis</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>CompoundingFrequency</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RoundingRule</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +575,29 @@
       <c r="I2" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>365</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,6 +635,29 @@
       <c r="I3" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>365</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -601,6 +695,29 @@
       <c r="I4" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>365</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -638,6 +755,29 @@
       <c r="I5" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>365</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -675,6 +815,29 @@
       <c r="I6" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>365</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -712,6 +875,29 @@
       <c r="I7" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>365</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -749,6 +935,29 @@
       <c r="I8" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>365</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -786,6 +995,29 @@
       <c r="I9" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>365</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -823,6 +1055,29 @@
       <c r="I10" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>365</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -860,6 +1115,29 @@
       <c r="I11" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>365</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -897,6 +1175,29 @@
       <c r="I12" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>365</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -934,6 +1235,29 @@
       <c r="I13" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>365</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -971,6 +1295,29 @@
       <c r="I14" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2021-07-30</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>365</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1008,6 +1355,29 @@
       <c r="I15" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2021-07-30</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>365</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1039,6 +1409,29 @@
       <c r="I16" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2021-07-30</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>365</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1070,6 +1463,29 @@
       <c r="I17" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2021-07-30</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>365</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1107,6 +1523,34 @@
       <c r="I18" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>365</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1144,6 +1588,34 @@
       <c r="I19" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>365</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1189,6 +1661,34 @@
       <c r="K20" s="2" t="n">
         <v>0.06</v>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>365</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1234,6 +1734,34 @@
       <c r="K21" s="2" t="n">
         <v>0.06</v>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>365</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1271,6 +1799,34 @@
       <c r="I22" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>365</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1308,6 +1864,34 @@
       <c r="I23" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>365</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1353,6 +1937,34 @@
       <c r="K24" s="2" t="n">
         <v>0.06</v>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>365</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1390,6 +2002,34 @@
       <c r="I25" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>365</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1427,6 +2067,34 @@
       <c r="I26" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>365</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1472,6 +2140,34 @@
       <c r="K27" s="2" t="n">
         <v>0.0688</v>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>365</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1507,7 +2203,35 @@
         <v>0.0999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.2999</v>
+        <v>0.36</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>365</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1544,7 +2268,35 @@
         <v>0.0999</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.2999</v>
+        <v>0.36</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>365</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1591,6 +2343,34 @@
       <c r="K30" s="2" t="n">
         <v>0.36</v>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>365</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1626,7 +2406,35 @@
         <v>0.0999</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.2999</v>
+        <v>0.36</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>365</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1663,7 +2471,35 @@
         <v>0.0999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.2999</v>
+        <v>0.36</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>365</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1710,6 +2546,34 @@
       <c r="K33" s="2" t="n">
         <v>0.06</v>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>PRIVATE</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>365</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1747,6 +2611,34 @@
       <c r="I34" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>365</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1784,6 +2676,34 @@
       <c r="I35" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>365</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1823,6 +2743,34 @@
       <c r="K36" s="2" t="n">
         <v>0.09</v>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>365</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1860,6 +2808,34 @@
       <c r="I37" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>365</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1897,6 +2873,34 @@
       <c r="I38" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>365</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1934,6 +2938,34 @@
       <c r="I39" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>365</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1971,6 +3003,34 @@
       <c r="I40" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>365</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2016,6 +3076,34 @@
       <c r="K41" s="2" t="n">
         <v>0.06</v>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>365</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2053,6 +3141,29 @@
       <c r="I42" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>365</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2090,6 +3201,29 @@
       <c r="I43" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>365</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2121,6 +3255,29 @@
       <c r="I44" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>365</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2158,6 +3315,29 @@
       <c r="I45" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>365</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2195,6 +3375,34 @@
       <c r="I46" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>COBRAND</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>365</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2232,6 +3440,34 @@
       <c r="I47" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>COBRAND</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>365</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2277,6 +3513,34 @@
       <c r="K48" s="2" t="n">
         <v>0.1199</v>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>COBRAND</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>365</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2314,6 +3578,34 @@
       <c r="I49" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>COBRAND</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>365</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2351,6 +3643,34 @@
       <c r="I50" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>365</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2388,6 +3708,34 @@
       <c r="I51" s="2" t="n">
         <v>0.2999</v>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>365</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2433,6 +3781,34 @@
       <c r="K52" s="2" t="n">
         <v>0.06</v>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>365</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2469,6 +3845,34 @@
       </c>
       <c r="I53" s="2" t="n">
         <v>0.2999</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>365</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>HALF_UP</t>
+        </is>
       </c>
     </row>
   </sheetData>
